--- a/artfynd/A 24253-2024 artfynd.xlsx
+++ b/artfynd/A 24253-2024 artfynd.xlsx
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117766521</v>
+        <v>117766525</v>
       </c>
       <c r="B6" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505306</v>
+        <v>505419</v>
       </c>
       <c r="R6" t="n">
-        <v>6862434</v>
+        <v>6862472</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117766527</v>
+        <v>117766521</v>
       </c>
       <c r="B7" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505470</v>
+        <v>505306</v>
       </c>
       <c r="R7" t="n">
-        <v>6862472</v>
+        <v>6862434</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117766525</v>
+        <v>117766527</v>
       </c>
       <c r="B8" t="n">
-        <v>78217</v>
+        <v>78218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505419</v>
+        <v>505470</v>
       </c>
       <c r="R8" t="n">
         <v>6862472</v>
